--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15760"/>
+    <workbookView windowHeight="15900"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>模块编号</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>1) 应发送包含重置链接的邮件；2) 重置链接应有效；3) 新密码应成功设置</t>
-  </si>
-  <si>
-    <t>6.2</t>
   </si>
   <si>
     <t>用户登录接口</t>
@@ -1370,7 +1367,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1396,7 +1393,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
@@ -1422,7 +1419,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -1447,81 +1444,81 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" t="s">
+      <c r="A5">
+        <v>5.5</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>31</v>
-      </c>
-      <c r="H5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>25</v>
+      <c r="A6">
+        <v>5.5</v>
       </c>
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>36</v>
       </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
       <c r="G6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" t="s">
         <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>25</v>
+      <c r="A7">
+        <v>5.5</v>
       </c>
       <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
       <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
         <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/test_data.xlsx
+++ b/test_data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15900"/>
+    <workbookView windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
